--- a/aq_files/0265.xlsx
+++ b/aq_files/0265.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI_MCQs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,678 +413,468 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Option A</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Details / Options</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option C</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Correct Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Why has AI become more practical in recent years?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Increase in computing power</t>
+          <t>What is Python mainly used for?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Decrease in interest</t>
+          <t>A) Web dev B) Data science C) Automation D) All</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lack of data</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Reduced algorithms</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>What role does big data play in AI growth?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Limits AI performance</t>
+          <t>Python is:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Provides training data</t>
+          <t>A) Compiled B) Interpreted C) Assembly D) Binary</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Reduces storage</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Eliminates need for AI</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Which hardware advancement boosted AI?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Typewriters</t>
+          <t>Which is correct Python file extension?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Quantum chips</t>
+          <t>A) .java B) .py C) .cpp D) .txt</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GPUs</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Floppy disks</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud computing helps AI by?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reducing internet</t>
+          <t>Python supports:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Providing scalable resources</t>
+          <t>A) OOP B) Functional C) Procedural D) All</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stopping data usage</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Limiting storage</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Why are algorithms improving AI?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>They are simpler</t>
+          <t>Python is known for:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>They process less data</t>
+          <t>A) Complex syntax B) Readability C) Speed only D) None</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>They are optimized for learning</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>They reduce accuracy</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI adoption increased due to?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Higher costs</t>
+          <t>Write a Python program to check if a number is even or odd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Business demand</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Less automation</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>No internet</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Which industry benefits most from AI now?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stone carving</t>
+          <t>Write a program to find the largest of 3 numbers.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Manual typing</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Paper making</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deep learning relies heavily on?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Small datasets</t>
+          <t>Write a program to calculate factorial using loop.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No data</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Large datasets</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Manual work</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Why is data availability important?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>To slow AI</t>
+          <t>Python was created by:</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>To train models</t>
+          <t>A) Dennis Ritchie B) Guido van Rossum C) James Gosling D) Elon Musk</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>To reduce accuracy</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>To avoid automation</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>What makes AI more accessible today?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>High costs</t>
+          <t>Python is dynamically typed means:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Open-source tools</t>
+          <t>A) Type declared B) Type decided at runtime C) No variables D) None</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lack of tools</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Limited internet</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Which company contributed to AI tools?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Write a program to reverse a number.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Local shop</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Library</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Bank only</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI is now used in?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Write a program to check palindrome number.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>All of the above</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Why is automation increasing?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AI capabilities improved</t>
+          <t>Write a program to print prime numbers up to N.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Less demand</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Higher errors</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Which factor reduced AI cost?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Better hardware</t>
+          <t>Python is case sensitive?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Manual work</t>
+          <t>A) Yes B) No C) Sometimes D) None</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Slow processing</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Paper usage</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>What is a key driver of AI success?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data + Compute</t>
+          <t>Which keyword defines function?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Less data</t>
+          <t>A) fun B) def C) function D) define</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No algorithms</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Manual systems</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Why do startups use AI?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>To avoid tech</t>
+          <t>Write a program to sum digits of a number.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>To scale quickly</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>To reduce growth</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>To avoid automation</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>B</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI growth is linked to?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Internet expansion</t>
+          <t>Write program to count digits in number.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Offline systems</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Manual tools</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Paper storage</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Which concept improved AI accuracy?</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Machine learning</t>
+          <t>Write program to swap two numbers without temp variable.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Handwriting</t>
+          <t>Write code and execute</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Typing</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Printing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Why is AI important now?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Solves complex problems</t>
+          <t>Python is open source?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Creates more problems</t>
+          <t>A) Yes B) No C) Partial D) None</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reduces efficiency</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Stops innovation</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>What trend supports AI rise?</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Digital transformation</t>
+          <t>Python supports indentation?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manual processes</t>
+          <t>A) Yes B) No C) Optional D) None</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Less connectivity</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Paper systems</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
